--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.03172522533206829</v>
       </c>
       <c r="C2" t="n">
-        <v>136680984</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>136680984</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>91061298</v>
+        <v>3675351</v>
       </c>
       <c r="L2" t="n">
-        <v>50501277</v>
+        <v>1793097</v>
       </c>
       <c r="M2" t="n">
-        <v>12354083</v>
+        <v>383554</v>
       </c>
       <c r="N2" t="n">
-        <v>641496</v>
+        <v>14506</v>
       </c>
       <c r="O2" t="n">
-        <v>7537160</v>
+        <v>245334</v>
       </c>
       <c r="P2" t="n">
-        <v>3121027</v>
+        <v>108077</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999063611030579</v>
+        <v>0.9998278021812439</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8438655138015747</v>
+        <v>0.7492419481277466</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7027998566627502</v>
+        <v>0.5487773418426514</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6133061051368713</v>
+        <v>0.4196433126926422</v>
       </c>
       <c r="U2" t="n">
-        <v>0.429197371006012</v>
+        <v>0.2146810740232468</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6722478866577148</v>
+        <v>0.4815673530101776</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7364239096641541</v>
+        <v>0.560934841632843</v>
       </c>
       <c r="X2" t="n">
-        <v>136680984</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>136680984</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>88913889</v>
+        <v>3625657</v>
       </c>
       <c r="AG2" t="n">
-        <v>46899072</v>
+        <v>1702389</v>
       </c>
       <c r="AH2" t="n">
-        <v>11279410</v>
+        <v>359888</v>
       </c>
       <c r="AI2" t="n">
-        <v>596760</v>
+        <v>13986</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6949069</v>
+        <v>229809</v>
       </c>
       <c r="AK2" t="n">
-        <v>2936983</v>
+        <v>101680</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8185003995895386</v>
+        <v>0.7342748641967773</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6653302311897278</v>
+        <v>0.5313179492950439</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5536076426506042</v>
+        <v>0.388602614402771</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3069254159927368</v>
+        <v>0.1582520604133606</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6217188835144043</v>
+        <v>0.4523318409919739</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6907645463943481</v>
+        <v>0.5261224508285522</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.008797159243656988</v>
       </c>
       <c r="C3" t="n">
-        <v>3983</v>
+        <v>379</v>
       </c>
       <c r="D3" t="n">
-        <v>91061298</v>
+        <v>3675351</v>
       </c>
       <c r="E3" t="n">
-        <v>15218043</v>
+        <v>1059578</v>
       </c>
       <c r="F3" t="n">
-        <v>860822</v>
+        <v>77365</v>
       </c>
       <c r="G3" t="n">
-        <v>104039</v>
+        <v>7536</v>
       </c>
       <c r="H3" t="n">
-        <v>81645</v>
+        <v>8986</v>
       </c>
       <c r="I3" t="n">
-        <v>12837</v>
+        <v>1467</v>
       </c>
       <c r="J3" t="n">
-        <v>216855018</v>
+        <v>9856558</v>
       </c>
       <c r="K3" t="n">
-        <v>229357704</v>
+        <v>10009663</v>
       </c>
       <c r="L3" t="n">
-        <v>260640848</v>
+        <v>11303629</v>
       </c>
       <c r="M3" t="n">
-        <v>325220386</v>
+        <v>14600262</v>
       </c>
       <c r="N3" t="n">
-        <v>350739245</v>
+        <v>15927942</v>
       </c>
       <c r="O3" t="n">
-        <v>338653590</v>
+        <v>15294638</v>
       </c>
       <c r="P3" t="n">
-        <v>348174534</v>
+        <v>15791999</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8483234047889709</v>
+        <v>0.7608379721641541</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7057986259460449</v>
+        <v>0.5446123480796814</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6014916896820068</v>
+        <v>0.4081699252128601</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3278944492340088</v>
+        <v>0.1622703969478607</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6717315912246704</v>
+        <v>0.479498565196991</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7331159114837646</v>
+        <v>0.5576584935188293</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>88913889</v>
+        <v>3625657</v>
       </c>
       <c r="Z3" t="n">
-        <v>16783353</v>
+        <v>1076099</v>
       </c>
       <c r="AA3" t="n">
-        <v>1175965</v>
+        <v>95172</v>
       </c>
       <c r="AB3" t="n">
-        <v>340578</v>
+        <v>19777</v>
       </c>
       <c r="AC3" t="n">
-        <v>109688</v>
+        <v>11762</v>
       </c>
       <c r="AD3" t="n">
-        <v>19194</v>
+        <v>2195</v>
       </c>
       <c r="AE3" t="n">
-        <v>216867816</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>226489786</v>
+        <v>9927657</v>
       </c>
       <c r="AG3" t="n">
-        <v>258405997</v>
+        <v>11276274</v>
       </c>
       <c r="AH3" t="n">
-        <v>323914758</v>
+        <v>14564488</v>
       </c>
       <c r="AI3" t="n">
-        <v>350244834</v>
+        <v>15906614</v>
       </c>
       <c r="AJ3" t="n">
-        <v>338100187</v>
+        <v>15280508</v>
       </c>
       <c r="AK3" t="n">
-        <v>347976789</v>
+        <v>15785012</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8283182382583618</v>
+        <v>0.7505507469177246</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6554547548294067</v>
+        <v>0.5170618891716003</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5491683483123779</v>
+        <v>0.3829850554466248</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3050280809402466</v>
+        <v>0.1564534604549408</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6193193197250366</v>
+        <v>0.4491553604602814</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6898847818374634</v>
+        <v>0.524651050567627</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.07250164964109351</v>
       </c>
       <c r="C4" t="n">
-        <v>1540</v>
+        <v>139</v>
       </c>
       <c r="D4" t="n">
-        <v>15593429</v>
+        <v>1117489</v>
       </c>
       <c r="E4" t="n">
-        <v>50501277</v>
+        <v>1793097</v>
       </c>
       <c r="F4" t="n">
-        <v>4466706</v>
+        <v>293313</v>
       </c>
       <c r="G4" t="n">
-        <v>186498</v>
+        <v>14128</v>
       </c>
       <c r="H4" t="n">
-        <v>698590</v>
+        <v>63591</v>
       </c>
       <c r="I4" t="n">
-        <v>103921</v>
+        <v>10671</v>
       </c>
       <c r="J4" t="n">
-        <v>12798</v>
+        <v>1070</v>
       </c>
       <c r="K4" t="n">
-        <v>16848429</v>
+        <v>1230075</v>
       </c>
       <c r="L4" t="n">
-        <v>21355991</v>
+        <v>1474343</v>
       </c>
       <c r="M4" t="n">
-        <v>7789338</v>
+        <v>530446</v>
       </c>
       <c r="N4" t="n">
-        <v>853145</v>
+        <v>53064</v>
       </c>
       <c r="O4" t="n">
-        <v>3674716</v>
+        <v>264115</v>
       </c>
       <c r="P4" t="n">
-        <v>1117058</v>
+        <v>84596</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999532103538513</v>
+        <v>0.9999138712882996</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8460885286331177</v>
+        <v>0.7549954652786255</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7042960524559021</v>
+        <v>0.5466868877410889</v>
       </c>
       <c r="T4" t="n">
-        <v>0.607341468334198</v>
+        <v>0.4138270914554596</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3717684745788574</v>
+        <v>0.1848321855068207</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6719896793365479</v>
+        <v>0.4805307388305664</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7347661852836609</v>
+        <v>0.5592918992042542</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>18134555</v>
+        <v>1177970</v>
       </c>
       <c r="Z4" t="n">
-        <v>46899072</v>
+        <v>1702389</v>
       </c>
       <c r="AA4" t="n">
-        <v>5181033</v>
+        <v>306468</v>
       </c>
       <c r="AB4" t="n">
-        <v>351756</v>
+        <v>21732</v>
       </c>
       <c r="AC4" t="n">
-        <v>851123</v>
+        <v>71063</v>
       </c>
       <c r="AD4" t="n">
-        <v>134422</v>
+        <v>12806</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>19716347</v>
+        <v>1312081</v>
       </c>
       <c r="AG4" t="n">
-        <v>23590842</v>
+        <v>1501698</v>
       </c>
       <c r="AH4" t="n">
-        <v>9094966</v>
+        <v>566220</v>
       </c>
       <c r="AI4" t="n">
-        <v>1347556</v>
+        <v>74392</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4228119</v>
+        <v>278245</v>
       </c>
       <c r="AK4" t="n">
-        <v>1314803</v>
+        <v>91583</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8233800530433655</v>
+        <v>0.742323637008667</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6603555679321289</v>
+        <v>0.524092972278595</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5513790249824524</v>
+        <v>0.3857733905315399</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3059738278388977</v>
+        <v>0.1573476195335388</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6205167770385742</v>
+        <v>0.4507379829883575</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6903243660926819</v>
+        <v>0.5253856778144836</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2434</v>
+        <v>202</v>
       </c>
       <c r="D5" t="n">
-        <v>891160</v>
+        <v>83500</v>
       </c>
       <c r="E5" t="n">
-        <v>4919071</v>
+        <v>312123</v>
       </c>
       <c r="F5" t="n">
-        <v>12354083</v>
+        <v>383554</v>
       </c>
       <c r="G5" t="n">
-        <v>307767</v>
+        <v>17238</v>
       </c>
       <c r="H5" t="n">
-        <v>1809044</v>
+        <v>120693</v>
       </c>
       <c r="I5" t="n">
-        <v>255517</v>
+        <v>22382</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>16281369</v>
+        <v>1155311</v>
       </c>
       <c r="L5" t="n">
-        <v>21050684</v>
+        <v>1499331</v>
       </c>
       <c r="M5" t="n">
-        <v>8184993</v>
+        <v>556138</v>
       </c>
       <c r="N5" t="n">
-        <v>1314914</v>
+        <v>74888</v>
       </c>
       <c r="O5" t="n">
-        <v>3683334</v>
+        <v>266313</v>
       </c>
       <c r="P5" t="n">
-        <v>1136181</v>
+        <v>85728</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999638199806213</v>
+        <v>0.9999334216117859</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9062935709953308</v>
+        <v>0.8515664935112</v>
       </c>
       <c r="S5" t="n">
-        <v>0.880054235458374</v>
+        <v>0.8149595260620117</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9548171758651733</v>
+        <v>0.9323859810829163</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9938676953315735</v>
+        <v>0.9920380115509033</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9791880249977112</v>
+        <v>0.9669934511184692</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936267733573914</v>
+        <v>0.9894014000892639</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1129897</v>
+        <v>99186</v>
       </c>
       <c r="Z5" t="n">
-        <v>5395878</v>
+        <v>313472</v>
       </c>
       <c r="AA5" t="n">
-        <v>11279410</v>
+        <v>359888</v>
       </c>
       <c r="AB5" t="n">
-        <v>367497</v>
+        <v>18421</v>
       </c>
       <c r="AC5" t="n">
-        <v>2056429</v>
+        <v>123791</v>
       </c>
       <c r="AD5" t="n">
-        <v>309965</v>
+        <v>24934</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>18428778</v>
+        <v>1205005</v>
       </c>
       <c r="AG5" t="n">
-        <v>24652889</v>
+        <v>1590039</v>
       </c>
       <c r="AH5" t="n">
-        <v>9259666</v>
+        <v>579804</v>
       </c>
       <c r="AI5" t="n">
-        <v>1359650</v>
+        <v>75408</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4271425</v>
+        <v>281838</v>
       </c>
       <c r="AK5" t="n">
-        <v>1320225</v>
+        <v>92125</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8921079039573669</v>
+        <v>0.8433712720870972</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8635443449020386</v>
+        <v>0.8076129555702209</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9480845928192139</v>
+        <v>0.9286872744560242</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9923427700996399</v>
+        <v>0.9906784892082214</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9759593605995178</v>
+        <v>0.9651481509208679</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9925469160079956</v>
+        <v>0.9885685443878174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>3293</v>
+        <v>232</v>
       </c>
       <c r="D6" t="n">
-        <v>267362</v>
+        <v>17264</v>
       </c>
       <c r="E6" t="n">
-        <v>372007</v>
+        <v>23335</v>
       </c>
       <c r="F6" t="n">
-        <v>397688</v>
+        <v>18099</v>
       </c>
       <c r="G6" t="n">
-        <v>641496</v>
+        <v>14506</v>
       </c>
       <c r="H6" t="n">
-        <v>232818</v>
+        <v>12925</v>
       </c>
       <c r="I6" t="n">
-        <v>41746</v>
+        <v>3033</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>311227</v>
+        <v>18527</v>
       </c>
       <c r="Z6" t="n">
-        <v>371365</v>
+        <v>22938</v>
       </c>
       <c r="AA6" t="n">
-        <v>376838</v>
+        <v>17926</v>
       </c>
       <c r="AB6" t="n">
-        <v>596760</v>
+        <v>13986</v>
       </c>
       <c r="AC6" t="n">
-        <v>252557</v>
+        <v>12833</v>
       </c>
       <c r="AD6" t="n">
-        <v>47663</v>
+        <v>3184</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>997</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>90560</v>
+        <v>11130</v>
       </c>
       <c r="E7" t="n">
-        <v>767527</v>
+        <v>70795</v>
       </c>
       <c r="F7" t="n">
-        <v>1898760</v>
+        <v>125842</v>
       </c>
       <c r="G7" t="n">
-        <v>222453</v>
+        <v>11420</v>
       </c>
       <c r="H7" t="n">
-        <v>7537160</v>
+        <v>245334</v>
       </c>
       <c r="I7" t="n">
-        <v>703037</v>
+        <v>47043</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>130366</v>
+        <v>15141</v>
       </c>
       <c r="Z7" t="n">
-        <v>937985</v>
+        <v>79076</v>
       </c>
       <c r="AA7" t="n">
-        <v>2151773</v>
+        <v>127747</v>
       </c>
       <c r="AB7" t="n">
-        <v>247742</v>
+        <v>11410</v>
       </c>
       <c r="AC7" t="n">
-        <v>6949069</v>
+        <v>229809</v>
       </c>
       <c r="AD7" t="n">
-        <v>803559</v>
+        <v>48464</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>551</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>5918</v>
+        <v>692</v>
       </c>
       <c r="E8" t="n">
-        <v>79343</v>
+        <v>8512</v>
       </c>
       <c r="F8" t="n">
-        <v>165362</v>
+        <v>15827</v>
       </c>
       <c r="G8" t="n">
-        <v>32388</v>
+        <v>2742</v>
       </c>
       <c r="H8" t="n">
-        <v>852619</v>
+        <v>57920</v>
       </c>
       <c r="I8" t="n">
-        <v>3121027</v>
+        <v>108077</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10302</v>
+        <v>1257</v>
       </c>
       <c r="Z8" t="n">
-        <v>102261</v>
+        <v>10113</v>
       </c>
       <c r="AA8" t="n">
-        <v>209357</v>
+        <v>18907</v>
       </c>
       <c r="AB8" t="n">
-        <v>39983</v>
+        <v>3052</v>
       </c>
       <c r="AC8" t="n">
-        <v>958322</v>
+        <v>58796</v>
       </c>
       <c r="AD8" t="n">
-        <v>2936983</v>
+        <v>101680</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
